--- a/Thread Chart/Seville Thread Charts.xlsx
+++ b/Thread Chart/Seville Thread Charts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fs1\InformationManagement\Procedures &amp; References\Embroidery Thread Charts\Completed\Seville\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF3D6ED-D226-445F-8CD6-565D2F60B780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0488D3EB-5180-48BF-B1B4-B20CE89F2A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22920" yWindow="-1095" windowWidth="29040" windowHeight="15840" xr2:uid="{70E4DF9C-6263-4B13-A151-CA2E71012314}"/>
+    <workbookView xWindow="34450" yWindow="-680" windowWidth="38620" windowHeight="21220" xr2:uid="{70E4DF9C-6263-4B13-A151-CA2E71012314}"/>
   </bookViews>
   <sheets>
     <sheet name="RA Super Brite Poly" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RA Super Brite Poly'!$A$1:$I$70</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -80,12 +80,12 @@
     <t>BlackC</t>
   </si>
   <si>
+    <t>Paris Blue</t>
+  </si>
+  <si>
     <t>Blues</t>
   </si>
   <si>
-    <t>Paris Blue</t>
-  </si>
-  <si>
     <t>Pastel Blue</t>
   </si>
   <si>
@@ -122,12 +122,12 @@
     <t>PN Navy</t>
   </si>
   <si>
+    <t>Seashell</t>
+  </si>
+  <si>
     <t>Browns</t>
   </si>
   <si>
-    <t>Seashell</t>
-  </si>
-  <si>
     <t>Beige</t>
   </si>
   <si>
@@ -149,12 +149,12 @@
     <t>Brown</t>
   </si>
   <si>
+    <t>Teardrop Grey</t>
+  </si>
+  <si>
     <t>Grays</t>
   </si>
   <si>
-    <t>Teardrop Grey</t>
-  </si>
-  <si>
     <t>Melville</t>
   </si>
   <si>
@@ -164,12 +164,12 @@
     <t>Decorator Tan</t>
   </si>
   <si>
+    <t>Bellaire Gray</t>
+  </si>
+  <si>
     <t>Cool Gray 9</t>
   </si>
   <si>
-    <t>Bellaire Gray</t>
-  </si>
-  <si>
     <t>Metal</t>
   </si>
   <si>
@@ -179,12 +179,12 @@
     <t>Black 7</t>
   </si>
   <si>
+    <t>Rolling Meadow</t>
+  </si>
+  <si>
     <t>Greens</t>
   </si>
   <si>
-    <t>Rolling Meadow</t>
-  </si>
-  <si>
     <t>Seafoam</t>
   </si>
   <si>
@@ -224,12 +224,12 @@
     <t>Green Petal</t>
   </si>
   <si>
+    <t>Golden Poppy</t>
+  </si>
+  <si>
     <t>Oranges</t>
   </si>
   <si>
-    <t>Golden Poppy</t>
-  </si>
-  <si>
     <t>Dark Texas Orange</t>
   </si>
   <si>
@@ -242,12 +242,12 @@
     <t>Honeysuckle</t>
   </si>
   <si>
+    <t>Opaline</t>
+  </si>
+  <si>
     <t>Pinks</t>
   </si>
   <si>
-    <t>Opaline</t>
-  </si>
-  <si>
     <t>475C</t>
   </si>
   <si>
@@ -263,12 +263,12 @@
     <t>New Berry</t>
   </si>
   <si>
+    <t>Cindy Purple</t>
+  </si>
+  <si>
     <t>Purples</t>
   </si>
   <si>
-    <t>Cindy Purple</t>
-  </si>
-  <si>
     <t>Purple</t>
   </si>
   <si>
@@ -278,12 +278,12 @@
     <t>Purple Accent</t>
   </si>
   <si>
+    <t>Radiant Red</t>
+  </si>
+  <si>
     <t>Reds</t>
   </si>
   <si>
-    <t>Radiant Red</t>
-  </si>
-  <si>
     <t>Foxy Red</t>
   </si>
   <si>
@@ -308,10 +308,10 @@
     <t>Trans. White</t>
   </si>
   <si>
+    <t>Maize</t>
+  </si>
+  <si>
     <t>Yellows</t>
-  </si>
-  <si>
-    <t>Maize</t>
   </si>
   <si>
     <t>Sunflower</t>
@@ -333,7 +333,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1343,8 +1343,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41F7C058-7381-4B3B-97C4-1BF7E2618390}">
-  <dimension ref="A1:I79"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O79"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="3" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" style="3" customWidth="1"/>
@@ -1352,14 +1352,14 @@
     <col min="4" max="4" width="19.7109375" style="72" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" style="3" customWidth="1"/>
-    <col min="7" max="9" width="8.85546875" style="3"/>
-    <col min="10" max="10" width="20.7109375" style="3" customWidth="1"/>
-    <col min="11" max="14" width="8.85546875" style="3"/>
-    <col min="15" max="15" width="50.7109375" style="3" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="3"/>
+    <col min="7" max="9" width="8.85546875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="3" hidden="1" customWidth="1"/>
+    <col min="11" max="14" width="8.85546875" style="3" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="50.7109375" style="3" hidden="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="50.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="50.1" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -1415,12 +1415,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="50.1" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>11</v>
@@ -1442,12 +1442,12 @@
         <v>233</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>11</v>
@@ -1469,12 +1469,12 @@
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>11</v>
@@ -1496,12 +1496,12 @@
         <v>231</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>11</v>
@@ -1523,12 +1523,12 @@
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="50.1" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>11</v>
@@ -1550,12 +1550,12 @@
         <v>189</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="50.1" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>11</v>
@@ -1577,12 +1577,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="50.1" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>11</v>
@@ -1604,12 +1604,12 @@
         <v>176</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="50.1" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>11</v>
@@ -1631,12 +1631,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="50.1" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>11</v>
@@ -1658,12 +1658,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="50.1" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>11</v>
@@ -1685,12 +1685,12 @@
         <v>147</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="50.1" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>11</v>
@@ -1712,12 +1712,12 @@
         <v>143</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="50.1" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>11</v>
@@ -1739,12 +1739,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="50.1" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>11</v>
@@ -1766,12 +1766,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="50.1" customHeight="1">
       <c r="A16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>11</v>
@@ -1793,12 +1793,12 @@
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="50.1" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>11</v>
@@ -1820,12 +1820,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="50.1" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>11</v>
@@ -1847,12 +1847,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="50.1" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>11</v>
@@ -1874,12 +1874,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="50.1" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>11</v>
@@ -1901,12 +1901,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="50.1" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>11</v>
@@ -1928,12 +1928,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="50.1" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>11</v>
@@ -1955,12 +1955,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="50.1" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>11</v>
@@ -1982,12 +1982,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="50.1" customHeight="1">
       <c r="A24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>11</v>
@@ -2009,12 +2009,12 @@
         <v>199</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="50.1" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>11</v>
@@ -2036,12 +2036,12 @@
         <v>169</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="50.1" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>11</v>
@@ -2063,12 +2063,12 @@
         <v>161</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="50.1" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>11</v>
@@ -2090,12 +2090,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="50.1" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>11</v>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E28" s="29"/>
       <c r="F28" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G28" s="3">
         <v>118</v>
@@ -2117,12 +2117,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="50.1" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>11</v>
@@ -2144,12 +2144,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="50.1" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>11</v>
@@ -2171,12 +2171,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="50.1" customHeight="1">
       <c r="A31" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>11</v>
@@ -2198,12 +2198,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="50.1" customHeight="1">
       <c r="A32" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>11</v>
@@ -2225,12 +2225,12 @@
         <v>194</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="50.1" customHeight="1">
       <c r="A33" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>11</v>
@@ -2252,12 +2252,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="50.1" customHeight="1">
       <c r="A34" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>11</v>
@@ -2279,12 +2279,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="50.1" customHeight="1">
       <c r="A35" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>11</v>
@@ -2306,12 +2306,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="50.1" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>52</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>11</v>
@@ -2333,12 +2333,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="50.1" customHeight="1">
       <c r="A37" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>11</v>
@@ -2360,12 +2360,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="50.1" customHeight="1">
       <c r="A38" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>11</v>
@@ -2387,12 +2387,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="50.1" customHeight="1">
       <c r="A39" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>11</v>
@@ -2414,12 +2414,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="50.1" customHeight="1">
       <c r="A40" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>11</v>
@@ -2441,12 +2441,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="50.1" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>11</v>
@@ -2468,12 +2468,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="50.1" customHeight="1">
       <c r="A42" s="3" t="s">
         <v>58</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>11</v>
@@ -2495,12 +2495,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="50.1" customHeight="1">
       <c r="A43" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>11</v>
@@ -2522,12 +2522,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="50.1" customHeight="1">
       <c r="A44" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>11</v>
@@ -2549,12 +2549,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="50.1" customHeight="1">
       <c r="A45" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>11</v>
@@ -2576,12 +2576,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="50.1" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>11</v>
@@ -2603,12 +2603,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="50.1" customHeight="1">
       <c r="A47" s="3" t="s">
         <v>64</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>11</v>
@@ -2630,12 +2630,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="50.1" customHeight="1">
       <c r="A48" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>11</v>
@@ -2657,12 +2657,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="50.1" customHeight="1">
       <c r="A49" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>11</v>
@@ -2684,12 +2684,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="50.1" customHeight="1">
       <c r="A50" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>11</v>
@@ -2711,12 +2711,12 @@
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="50.1" customHeight="1">
       <c r="A51" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>11</v>
@@ -2738,12 +2738,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="50.1" customHeight="1">
       <c r="A52" s="3" t="s">
         <v>71</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>11</v>
@@ -2765,12 +2765,12 @@
         <v>148</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="50.1" customHeight="1">
       <c r="A53" s="3" t="s">
         <v>73</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>11</v>
@@ -2792,12 +2792,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="50.1" customHeight="1">
       <c r="A54" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>11</v>
@@ -2819,12 +2819,12 @@
         <v>187</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="50.1" customHeight="1">
       <c r="A55" s="3" t="s">
         <v>76</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>11</v>
@@ -2846,12 +2846,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="50.1" customHeight="1">
       <c r="A56" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>11</v>
@@ -2873,12 +2873,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="50.1" customHeight="1">
       <c r="A57" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>11</v>
@@ -2900,12 +2900,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="50.1" customHeight="1">
       <c r="A58" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>11</v>
@@ -2927,12 +2927,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="50.1" customHeight="1">
       <c r="A59" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>11</v>
@@ -2954,12 +2954,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="50.1" customHeight="1">
       <c r="A60" s="3" t="s">
         <v>82</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>11</v>
@@ -2981,12 +2981,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="50.1" customHeight="1">
       <c r="A61" s="3" t="s">
         <v>83</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>11</v>
@@ -3008,12 +3008,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="50.1" customHeight="1">
       <c r="A62" s="3" t="s">
         <v>84</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>11</v>
@@ -3035,12 +3035,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="50.1" customHeight="1">
       <c r="A63" s="3" t="s">
         <v>85</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>11</v>
@@ -3062,7 +3062,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="50.1" customHeight="1">
       <c r="A64" s="3" t="s">
         <v>86</v>
       </c>
@@ -3089,12 +3089,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="50.1" customHeight="1">
       <c r="A65" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>11</v>
@@ -3116,12 +3116,12 @@
         <v>162</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="50.1" customHeight="1">
       <c r="A66" s="3" t="s">
         <v>91</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>11</v>
@@ -3143,12 +3143,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="50.1" customHeight="1">
       <c r="A67" s="3" t="s">
         <v>92</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>11</v>
@@ -3170,12 +3170,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="50.1" customHeight="1">
       <c r="A68" s="3" t="s">
         <v>93</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>11</v>
@@ -3197,12 +3197,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="50.1" customHeight="1">
       <c r="A69" s="3" t="s">
         <v>94</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>11</v>
@@ -3224,12 +3224,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="50.1" customHeight="1">
       <c r="A70" s="3" t="s">
         <v>95</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>11</v>
@@ -3251,21 +3251,242 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="72" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="73" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="74" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="75" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="76" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="77" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="78" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="79" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="sAt4nm7F20pXqJiAi/VxZwwZ+XSC4s2DGD8z63xDWNKaqrziFwb6bgu3jL369VPIUL+nJp841PIhXL6mgjdr2A==" saltValue="+hu6Bh2FLk3mvjLMowJCdQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection sort="0" autoFilter="0"/>
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="uoNtGRLPMOTNKQow58490YHrqT5n5J60NrNjmI6CdRSh6ils3oJbZJl/oqFLeh0HjlEKQarwv0SyQeYJy0ZmhA==" saltValue="4Bk8FzUXT9j8w/DqUK+fRg==" spinCount="100000" sqref="A1:I70" name="AllowSortFilter"/>
   </protectedRanges>
   <autoFilter ref="A1:I70" xr:uid="{41F7C058-7381-4B3B-97C4-1BF7E2618390}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A1C7DD37AE641E4B9B3FD2F75B2D99BC" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6b9cb41f595aff4764e09aef2b23c1ed">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ea7a09a4-fe73-437e-8a86-996460e9b058" xmlns:ns3="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="daad8a4a6daff5298e6b89d91afce8e3" ns2:_="" ns3:_="">
+    <xsd:import namespace="ea7a09a4-fe73-437e-8a86-996460e9b058"/>
+    <xsd:import namespace="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ea7a09a4-fe73-437e-8a86-996460e9b058" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d2f5926c-fefe-46c4-85d9-9ef0eea46f5c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{6fbb2a74-2168-4404-a595-59f9a11d4eed}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea7a09a4-fe73-437e-8a86-996460e9b058">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D73C32F-6FBA-45C9-AD15-2E099FDCE855}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EF2BC90-637E-4466-900C-AE511DBB786D}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D45CA74B-2E7B-4692-B17F-9B0CC5BAA777}"/>
 </file>